--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Carolina-Floor- Systems\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Carolina-Floor-Systems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D1D140-2E98-4B20-9A2F-C33D733D664D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CB5454-FBC5-4D84-B710-6A89121915AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20598,7 +20598,7 @@
         <v>46176.466319444444</v>
       </c>
       <c r="J727">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K727" t="s">
         <v>11</v>
@@ -20627,7 +20627,7 @@
         <v>46176.466319444444</v>
       </c>
       <c r="J728">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K728" t="s">
         <v>11</v>
@@ -20656,7 +20656,7 @@
         <v>46176.467013888891</v>
       </c>
       <c r="J729">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K729" t="s">
         <v>11</v>
@@ -20676,16 +20676,16 @@
         <v>30</v>
       </c>
       <c r="G730" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H730">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H730" s="2">
+        <v>8.3912037037037045E-3</v>
       </c>
       <c r="I730" s="1">
         <v>46176.467013888891</v>
       </c>
       <c r="J730">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K730" t="s">
         <v>11</v>
@@ -20714,7 +20714,7 @@
         <v>46176.467013888891</v>
       </c>
       <c r="J731">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K731" t="s">
         <v>11</v>
@@ -20743,7 +20743,7 @@
         <v>46176.46770833333</v>
       </c>
       <c r="J732">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K732" t="s">
         <v>11</v>
@@ -20772,7 +20772,7 @@
         <v>46176.46770833333</v>
       </c>
       <c r="J733">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K733" t="s">
         <v>11</v>
@@ -20801,7 +20801,7 @@
         <v>46176.468402777777</v>
       </c>
       <c r="J734">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K734" t="s">
         <v>11</v>
@@ -20830,7 +20830,7 @@
         <v>46176.468402777777</v>
       </c>
       <c r="J735">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K735" t="s">
         <v>11</v>
@@ -20859,7 +20859,7 @@
         <v>46176.469097222223</v>
       </c>
       <c r="J736">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K736" t="s">
         <v>11</v>
@@ -20888,7 +20888,7 @@
         <v>46176.469097222223</v>
       </c>
       <c r="J737">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K737" t="s">
         <v>11</v>
@@ -20917,7 +20917,7 @@
         <v>46176.469097222223</v>
       </c>
       <c r="J738">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K738" t="s">
         <v>11</v>
@@ -20946,7 +20946,7 @@
         <v>46176.46979166667</v>
       </c>
       <c r="J739">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K739" t="s">
         <v>11</v>
@@ -20975,7 +20975,7 @@
         <v>46176.46979166667</v>
       </c>
       <c r="J740">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K740" t="s">
         <v>11</v>
@@ -21004,7 +21004,7 @@
         <v>46176.470486111109</v>
       </c>
       <c r="J741">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K741" t="s">
         <v>11</v>
@@ -21033,7 +21033,7 @@
         <v>46176.470486111109</v>
       </c>
       <c r="J742">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K742" t="s">
         <v>11</v>
@@ -21062,7 +21062,7 @@
         <v>46176.470486111109</v>
       </c>
       <c r="J743">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K743" t="s">
         <v>11</v>
@@ -21091,7 +21091,7 @@
         <v>46176.471180555556</v>
       </c>
       <c r="J744">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K744" t="s">
         <v>11</v>
@@ -21120,7 +21120,7 @@
         <v>46176.471180555556</v>
       </c>
       <c r="J745">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K745" t="s">
         <v>11</v>
@@ -21149,7 +21149,7 @@
         <v>46176.471180555556</v>
       </c>
       <c r="J746">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K746" t="s">
         <v>11</v>
@@ -21178,7 +21178,7 @@
         <v>46176.471875000003</v>
       </c>
       <c r="J747">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K747" t="s">
         <v>11</v>
@@ -21207,7 +21207,7 @@
         <v>46176.471875000003</v>
       </c>
       <c r="J748">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K748" t="s">
         <v>11</v>
@@ -21236,7 +21236,7 @@
         <v>46176.472569444442</v>
       </c>
       <c r="J749">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K749" t="s">
         <v>11</v>
@@ -21265,7 +21265,7 @@
         <v>46176.472569444442</v>
       </c>
       <c r="J750">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K750" t="s">
         <v>11</v>
@@ -21294,7 +21294,7 @@
         <v>46176.472569444442</v>
       </c>
       <c r="J751">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K751" t="s">
         <v>11</v>
@@ -21323,7 +21323,7 @@
         <v>46176.473263888889</v>
       </c>
       <c r="J752">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K752" t="s">
         <v>11</v>
@@ -21352,7 +21352,7 @@
         <v>46176.473263888889</v>
       </c>
       <c r="J753">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K753" t="s">
         <v>11</v>
@@ -21381,7 +21381,7 @@
         <v>46176.473263888889</v>
       </c>
       <c r="J754">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K754" t="s">
         <v>11</v>
@@ -21439,7 +21439,7 @@
         <v>46176.473958333336</v>
       </c>
       <c r="J756">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K756" t="s">
         <v>11</v>
@@ -21468,7 +21468,7 @@
         <v>46176.473958333336</v>
       </c>
       <c r="J757">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K757" t="s">
         <v>11</v>
@@ -21497,7 +21497,7 @@
         <v>46176.474652777775</v>
       </c>
       <c r="J758">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K758" t="s">
         <v>11</v>
